--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,9 +790,3740 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136707271</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>53</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>325575</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6556374</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707271</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136707276</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>53</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>325580</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6556454</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707276</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136707278</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>325586</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6556476</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707278</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136707280</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97583</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>325578</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6556500</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707280</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136707270</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92106</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>325604</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6556372</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707270</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136707272</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97619</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2590</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kornknutmossa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odontoschisma denudatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Mart.) Dumort</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>325575</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6556374</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707272</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136707299</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96662</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2666</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grov fjädermossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Exsertotheca crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>325519</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6556576</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707299</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136707266</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>325595</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556462</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136707273</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93404</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>325518</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6556389</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707273</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136707284</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>325570</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6556535</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707284</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136707265</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>325611</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6556513</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707265</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>136707295</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79474</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>325550</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6556576</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707295</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>136707267</v>
+      </c>
+      <c r="B15" t="n">
+        <v>75564</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>325623</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6556383</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707267</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136707286</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75564</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>325557</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6556515</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707286</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136707287</v>
+      </c>
+      <c r="B17" t="n">
+        <v>75564</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>325547</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6556511</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707287</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136707289</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75564</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>325542</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6556502</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707289</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136707291</v>
+      </c>
+      <c r="B19" t="n">
+        <v>75564</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>325541</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6556540</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707291</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136707277</v>
+      </c>
+      <c r="B20" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>325584</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6556459</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707277</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>136707304</v>
+      </c>
+      <c r="B21" t="n">
+        <v>4777</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>325533</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6556617</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707304</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>136707269</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>325620</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6556364</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707269</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>136707274</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>325584</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6556428</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707274</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>136707282</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>325579</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6556526</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707282</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>136707288</v>
+      </c>
+      <c r="B25" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>325541</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6556506</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707288</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>136707300</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5182</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>325532</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6556612</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707300</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>136707268</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>325620</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6556364</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707268</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>136707275</v>
+      </c>
+      <c r="B28" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>325584</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6556428</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707275</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136707279</v>
+      </c>
+      <c r="B29" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>325578</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6556500</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707279</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136707281</v>
+      </c>
+      <c r="B30" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>325579</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6556526</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707281</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136707285</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>325562</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6556528</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707285</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136707292</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>325541</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6556540</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707292</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136707294</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>325553</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6556564</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707294</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136707302</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5202</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mellanfjällen, Dls</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>325533</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6556617</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Dals-Ed</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nössemark</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136707302</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97619</v>
+        <v>97624</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96662</v>
+        <v>96667</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>136707267</v>
       </c>
       <c r="B15" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136707286</v>
       </c>
       <c r="B16" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136707287</v>
       </c>
       <c r="B17" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136707289</v>
       </c>
       <c r="B18" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136707291</v>
       </c>
       <c r="B19" t="n">
-        <v>75564</v>
+        <v>75566</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97624</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96667</v>
+        <v>96669</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96669</v>
+        <v>96675</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96675</v>
+        <v>96677</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96677</v>
+        <v>96678</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96678</v>
+        <v>96684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96684</v>
+        <v>96688</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96688</v>
+        <v>96690</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96690</v>
+        <v>96692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96692</v>
+        <v>96705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>136707267</v>
       </c>
       <c r="B15" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136707286</v>
       </c>
       <c r="B16" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136707287</v>
       </c>
       <c r="B17" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136707289</v>
       </c>
       <c r="B18" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136707291</v>
       </c>
       <c r="B19" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>136707267</v>
       </c>
       <c r="B15" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136707286</v>
       </c>
       <c r="B16" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136707287</v>
       </c>
       <c r="B17" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136707289</v>
       </c>
       <c r="B18" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136707291</v>
       </c>
       <c r="B19" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -2690,11 +2690,7 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -2812,11 +2808,7 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -2934,11 +2926,7 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3056,11 +3044,7 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3178,11 +3162,7 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3300,11 +3280,7 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3422,11 +3398,7 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3544,11 +3516,7 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3666,11 +3634,7 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3788,11 +3752,7 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -3910,11 +3870,7 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -4032,11 +3988,7 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -4154,11 +4106,7 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -4276,11 +4224,7 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>
@@ -4398,11 +4342,7 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Mellanfjällen, Dls</t>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96707</v>
+        <v>96710</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 22946-2026 artfynd.xlsx
+++ b/artfynd/A 22946-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136707271</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136707276</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>136707278</v>
       </c>
       <c r="B5" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>136707280</v>
       </c>
       <c r="B6" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>136707270</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1335,7 +1335,7 @@
         <v>136707272</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         <v>136707299</v>
       </c>
       <c r="B9" t="n">
-        <v>96710</v>
+        <v>96720</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>136707266</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>136707273</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>136707284</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>136707265</v>
       </c>
       <c r="B13" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1962,7 +1962,7 @@
         <v>136707295</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2079,7 +2079,7 @@
         <v>136707267</v>
       </c>
       <c r="B15" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         <v>136707286</v>
       </c>
       <c r="B16" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
         <v>136707287</v>
       </c>
       <c r="B17" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>136707289</v>
       </c>
       <c r="B18" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>136707291</v>
       </c>
       <c r="B19" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>136707277</v>
       </c>
       <c r="B20" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>136707304</v>
       </c>
       <c r="B21" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>136707269</v>
       </c>
       <c r="B22" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>136707274</v>
       </c>
       <c r="B23" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>136707282</v>
       </c>
       <c r="B24" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>136707288</v>
       </c>
       <c r="B25" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3372,7 +3372,7 @@
         <v>136707300</v>
       </c>
       <c r="B26" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         <v>136707268</v>
       </c>
       <c r="B27" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3608,7 +3608,7 @@
         <v>136707275</v>
       </c>
       <c r="B28" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3726,7 +3726,7 @@
         <v>136707279</v>
       </c>
       <c r="B29" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3844,7 +3844,7 @@
         <v>136707281</v>
       </c>
       <c r="B30" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>136707285</v>
       </c>
       <c r="B31" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>136707292</v>
       </c>
       <c r="B32" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         <v>136707294</v>
       </c>
       <c r="B33" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4316,7 +4316,7 @@
         <v>136707302</v>
       </c>
       <c r="B34" t="n">
-        <v>5202</v>
+        <v>5208</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
